--- a/backend/public/templates/template_laporan.xlsx
+++ b/backend/public/templates/template_laporan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project KP\KpLintasDataMultimedia\backend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5D1CAF-C40A-455E-A13D-240E2DA289F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69082EA9-B7B6-4726-8F48-4A7507A094C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{86B2E292-7102-480D-94E1-BC27227BEAC2}"/>
   </bookViews>
@@ -74,9 +74,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-[$Rp-3809]* #,##0.00_-;\-[$Rp-3809]* #,##0.00_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$Rp-3809]* #,##0.00_-;\-[$Rp-3809]* #,##0.00_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +111,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -126,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -134,28 +142,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency [0]" xfId="1" builtinId="7"/>
@@ -179,15 +216,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>375987</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1286578</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>121016</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>50131</xdr:rowOff>
+      <xdr:rowOff>25064</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -216,8 +253,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1" y="1"/>
-          <a:ext cx="1896177" cy="1190624"/>
+          <a:off x="375987" y="0"/>
+          <a:ext cx="1900687" cy="1178090"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -529,50 +566,54 @@
   <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="5"/>
-    <col min="2" max="2" width="23.140625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="67.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="27" style="5" customWidth="1"/>
-    <col min="8" max="8" width="55.28515625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="27.42578125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="23.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="67.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="56.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="27" style="3" customWidth="1"/>
+    <col min="8" max="8" width="37.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="3" t="s">
+    <row r="4" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
         <f>SUM(Data_Pemasukan!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="6">
+      <c r="C8" s="5"/>
+      <c r="D8" s="4">
         <f>SUM(Data_Pengeluaran!C:C)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f>B8-D8</f>
         <v>0</v>
       </c>
